--- a/05_Current_Prototype/data/examples/site/electrical-bad-sample.xlsx
+++ b/05_Current_Prototype/data/examples/site/electrical-bad-sample.xlsx
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>91.59999999999999</v>
+        <v>25.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.99</v>
+        <v>9.26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45881.42</v>
+        <v>45875.49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
